--- a/Documents/Monitoring_Sheets/MAED_Monitoring_Sheet.xlsx
+++ b/Documents/Monitoring_Sheets/MAED_Monitoring_Sheet.xlsx
@@ -437,13 +437,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF16"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,17 +651,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ESCOBAR</t>
+          <t>FLORES</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CLARISSE</t>
+          <t>ISABEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>GS-2026-0008</t>
+          <t>GS-2026-0007</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -727,6 +728,36 @@
       </c>
       <c r="Z5" t="n">
         <v>54</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Graduation candidate</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -735,17 +766,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GONZALES</t>
+          <t>MENDOZA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GIAN</t>
+          <t>ELENA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GS-2026-0003</t>
+          <t>GS-2026-0011</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -754,7 +785,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>3</v>
@@ -771,8 +802,53 @@
       <c r="L6" t="n">
         <v>3</v>
       </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>3</v>
+      </c>
       <c r="Z6" t="n">
-        <v>15</v>
+        <v>45</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>No-subject residency</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -781,17 +857,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NAVARRO</t>
+          <t>YU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CAMILLE</t>
+          <t>MIGUEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>GS-2026-0001</t>
+          <t>GS-2026-0004</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -869,33 +945,58 @@
           <t>X</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Thesis / Final Defense</t>
+        </is>
+      </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>23-24</t>
+        </is>
+      </c>
       <c r="B8" t="n">
         <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LARA</t>
+          <t>PAULO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GS-2026-0007</t>
+          <t>GS-2026-0010</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MAED-T</t>
+          <t>MAED-NT</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -915,58 +1016,12 @@
       <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="N8" t="n">
-        <v>3</v>
-      </c>
-      <c r="O8" t="n">
-        <v>3</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3</v>
-      </c>
       <c r="Z8" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>X</t>
+        <v>18</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>AWOL declared</t>
         </is>
       </c>
     </row>
@@ -976,22 +1031,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>YU</t>
+          <t>LIM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MIGUEL</t>
+          <t>ADRIAN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GS-2026-0004</t>
+          <t>GS-2026-0006</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MAED-T</t>
+          <t>MAED-NT</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1033,80 +1088,37 @@
       <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3</v>
-      </c>
       <c r="Z9" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>X</t>
+        <v>36</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Withdrawal request</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>23-24</t>
-        </is>
-      </c>
       <c r="B10" t="n">
         <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AQUINO</t>
+          <t>ONG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ISABEL</t>
+          <t>HECTOR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>GS-2026-0006</t>
+          <t>GS-2026-0008</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MAED-T</t>
+          <t>MAED-NT</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1169,24 +1181,34 @@
       <c r="Z10" t="n">
         <v>54</v>
       </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Practicum in progress</t>
+        </is>
+      </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>24-25</t>
+        </is>
+      </c>
       <c r="B11" t="n">
         <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AQUINO</t>
+          <t>DELA CRUZ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HECTOR</t>
+          <t>MARIA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>GS-2026-0012</t>
+          <t>GS-2026-0009</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1224,49 +1246,12 @@
       <c r="P11" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3</v>
-      </c>
       <c r="Z11" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>X</t>
+        <v>27</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Readmission after LOA</t>
         </is>
       </c>
     </row>
@@ -1276,26 +1261,26 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>SANTOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CLARISSE</t>
+          <t>BENJAMIN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GS-2026-0010</t>
+          <t>GS-2026-0003</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MAED-T</t>
+          <t>MAED-NT</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>3</v>
@@ -1312,8 +1297,25 @@
       <c r="L12" t="n">
         <v>3</v>
       </c>
+      <c r="M12" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3</v>
+      </c>
       <c r="Z12" t="n">
-        <v>15</v>
+        <v>27</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Leave of absence applicant</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1322,12 +1324,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ONG</t>
+          <t>TAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ELISE</t>
+          <t>CLARISSE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1337,11 +1339,11 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MAED-T</t>
+          <t>MAED-NT</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>3</v>
@@ -1361,50 +1363,19 @@
       <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3</v>
-      </c>
       <c r="Z13" t="n">
-        <v>54</v>
+        <v>18</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>AWOL - return request</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24-25</t>
+          <t>25-26</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1412,17 +1383,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FLORES</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GRACE</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GS-2026-0011</t>
+          <t>GS-2026-0001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1433,23 +1404,13 @@
       <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
       <c r="Z14" t="n">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>New student handoff</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1458,22 +1419,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MENDOZA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>GRACE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GS-2026-0009</t>
+          <t>GS-2026-0002</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MAED-T</t>
+          <t>MAED-NT</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1488,118 +1449,12 @@
       <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
       <c r="Z15" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>25-26</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CASTILLO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>MARIELLE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>GS-2026-0002</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>MAED-T</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I16" t="n">
-        <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>54</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>X</t>
+        <v>9</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Needs enrollment</t>
         </is>
       </c>
     </row>

--- a/Documents/Monitoring_Sheets/MAED_Monitoring_Sheet.xlsx
+++ b/Documents/Monitoring_Sheets/MAED_Monitoring_Sheet.xlsx
@@ -832,8 +832,17 @@
       <c r="V6" t="n">
         <v>3</v>
       </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3</v>
+      </c>
       <c r="Z6" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
